--- a/STMS_code/dist/매출.xlsx
+++ b/STMS_code/dist/매출.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ORIFICE_PLATE_D0.3*TUBE 1/4_SUS304_NONE</t>
+          <t>Orifice, Tube Type, D0.3 Tube 1/4</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RETAINER_BEARING_5208_S45C_NONE</t>
+          <t>Retainer, HD DE Bearing, S45C</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SLINGER_ID50.0OD77.4L30.9_SUM24L_NONE</t>
+          <t>Slinger, HD550 Rev1 Gear Side</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -715,7 +715,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SLINGER_ID40.02OD49.6L15.240_12L14_NONE</t>
+          <t>Slinger, HD DE, 15.240±0.005</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -738,7 +738,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LOCK NUT_FORCED DRIVE_M45X1.5P_S45C_NONE</t>
+          <t>LOCK NUT_FORCED DRIVE_M45X1.5P</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -853,7 +853,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>RING_LABYRINTH_ID50.00OD70.00L11.2_S45C_NONE</t>
+          <t>RING_LABYRINTH_ID50.00*OD70.00*L11.2_S45C_NONE</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OIL GUIDE_TONGUE SHIM*NON DRIVE_SS400_NONE</t>
+          <t>Tongue Shim-L, MK3000</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KEY_MOTOR ROTATOR_RD900_S45C_NONE</t>
+          <t>Key, RD900 22kW Rotator</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SPACER_MOTOR ROTATOR_S45C_NONE</t>
+          <t>Ring, RD900/MK3000 Motor Rotator Spacer</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PLATE_BYPASS_RD900_2-4 STAGE_SUS304_NONE</t>
+          <t>Plate, RD900 Bypass 2-4 Stage</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RETAINER_BEARING_5208_S45C_NONE</t>
+          <t>Retainer, HD DE Bearing, S45C</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SLINGER_ID50.0OD77.4L30.9_SUM24L_NONE</t>
+          <t>Slinger, HD550 Rev1 Gear Side</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SLINGER_ID40.02OD49.6L15.240_12L14_NONE</t>
+          <t>Slinger, HD DE, 15.240±0.005</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RING_LABYRINTH_ID50.00OD70.00L11.2_S45C_NONE</t>
+          <t>RING_LABYRINTH_ID50.00*OD70.00*L11.2_S45C_NONE</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ORIFICE_PLATE_D0.3*TUBE 1/4_SUS304_NONE</t>
+          <t>Orifice, Tube Type, D0.3 Tube 1/4</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>LOCK NUT_FORCED DRIVE_M45X1.5P_S45C_NONE</t>
+          <t>LOCK NUT_FORCED DRIVE_M45X1.5P</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OIL GUIDE_TONGUE SHIM*NON DRIVE_SS400_NONE</t>
+          <t>Tongue Shim-L, MK3000</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KEY_MOTOR ROTATOR_RD900_S45C_NONE</t>
+          <t>Key, RD900 22kW Rotator</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SPACER_MOTOR ROTATOR_S45C_NONE</t>
+          <t>Ring, RD900/MK3000 Motor Rotator Spacer</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>PLATE_BYPASS_RD900_2-4 STAGE_SUS304_NONE</t>
+          <t>Plate, RD900 Bypass 2-4 Stage</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>ORIFICE_PLATE_D0.3*TUBE 1/4_SUS304_NONE</t>
+          <t>Orifice, Tube Type, D0.3 Tube 1/4</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RETAINER_BEARING_5208_S45C_NONE</t>
+          <t>Retainer, HD DE Bearing, S45C</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>SLINGER_ID50.0OD77.4L30.9_SUM24L_NONE</t>
+          <t>Slinger, HD550 Rev1 Gear Side</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SLINGER_ID40.02OD49.6L15.240_12L14_NONE</t>
+          <t>Slinger, HD DE, 15.240±0.005</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>LOCK NUT_FORCED DRIVE_M45X1.5P_S45C_NONE</t>
+          <t>LOCK NUT_FORCED DRIVE_M45X1.5P</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>RING_LABYRINTH_ID50.00OD70.00L11.2_S45C_NONE</t>
+          <t>RING_LABYRINTH_ID50.00*OD70.00*L11.2_S45C_NONE</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>OIL GUIDE_TONGUE SHIM*NON DRIVE_SS400_NONE</t>
+          <t>Tongue Shim-L, MK3000</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>KEY_MOTOR ROTATOR_RD900_S45C_NONE</t>
+          <t>Key, RD900 22kW Rotator</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>SPACER_MOTOR ROTATOR_S45C_NONE</t>
+          <t>Ring, RD900/MK3000 Motor Rotator Spacer</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>PLATE_BYPASS_RD900_2-4 STAGE_SUS304_NONE</t>
+          <t>Plate, RD900 Bypass 2-4 Stage</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>RETAINER_BEARING_5208_S45C_NONE</t>
+          <t>Retainer, HD DE Bearing, S45C</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>SLINGER_ID50.0OD77.4L30.9_SUM24L_NONE</t>
+          <t>Slinger, HD550 Rev1 Gear Side</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>ORIFICE_PLATE_D0.3*TUBE 1/4_SUS304_NONE</t>
+          <t>Orifice, Tube Type, D0.3 Tube 1/4</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>SLINGER_ID40.02OD49.6L15.240_12L14_NONE</t>
+          <t>Slinger, HD DE, 15.240±0.005</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>LOCK NUT_FORCED DRIVE_M45X1.5P_S45C_NONE</t>
+          <t>LOCK NUT_FORCED DRIVE_M45X1.5P</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>RING_LABYRINTH_ID50.00OD70.00L11.2_S45C_NONE</t>
+          <t>RING_LABYRINTH_ID50.00*OD70.00*L11.2_S45C_NONE</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>OIL GUIDE_TONGUE SHIM*NON DRIVE_SS400_NONE</t>
+          <t>Tongue Shim-L, MK3000</t>
         </is>
       </c>
       <c r="D246" t="n">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>KEY_MOTOR ROTATOR_RD900_S45C_NONE</t>
+          <t>Key, RD900 22kW Rotator</t>
         </is>
       </c>
       <c r="D259" t="n">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>SPACER_MOTOR ROTATOR_S45C_NONE</t>
+          <t>Ring, RD900/MK3000 Motor Rotator Spacer</t>
         </is>
       </c>
       <c r="D260" t="n">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>PLATE_BYPASS_RD900_2-4 STAGE_SUS304_NONE</t>
+          <t>Plate, RD900 Bypass 2-4 Stage</t>
         </is>
       </c>
       <c r="D262" t="n">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>RETAINER_BEARING_5208_S45C_NONE</t>
+          <t>Retainer, HD DE Bearing, S45C</t>
         </is>
       </c>
       <c r="D292" t="n">
@@ -7247,7 +7247,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>ORIFICE_PLATE_D0.3*TUBE 1/4_SUS304_NONE</t>
+          <t>Orifice, Tube Type, D0.3 Tube 1/4</t>
         </is>
       </c>
       <c r="D297" t="n">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>SLINGER_ID50.0OD77.4L30.9_SUM24L_NONE</t>
+          <t>Slinger, HD550 Rev1 Gear Side</t>
         </is>
       </c>
       <c r="D299" t="n">
@@ -7362,7 +7362,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>SLINGER_ID40.02OD49.6L15.240_12L14_NONE</t>
+          <t>Slinger, HD DE, 15.240±0.005</t>
         </is>
       </c>
       <c r="D302" t="n">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>LOCK NUT_FORCED DRIVE_M45X1.5P_S45C_NONE</t>
+          <t>LOCK NUT_FORCED DRIVE_M45X1.5P</t>
         </is>
       </c>
       <c r="D304" t="n">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>RING_LABYRINTH_ID50.00OD70.00L11.2_S45C_NONE</t>
+          <t>RING_LABYRINTH_ID50.00*OD70.00*L11.2_S45C_NONE</t>
         </is>
       </c>
       <c r="D309" t="n">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>OIL GUIDE_TONGUE SHIM*NON DRIVE_SS400_NONE</t>
+          <t>Tongue Shim-L, MK3000</t>
         </is>
       </c>
       <c r="D318" t="n">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>KEY_MOTOR ROTATOR_RD900_S45C_NONE</t>
+          <t>Key, RD900 22kW Rotator</t>
         </is>
       </c>
       <c r="D331" t="n">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>SPACER_MOTOR ROTATOR_S45C_NONE</t>
+          <t>Ring, RD900/MK3000 Motor Rotator Spacer</t>
         </is>
       </c>
       <c r="D332" t="n">
@@ -8098,7 +8098,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>PLATE_BYPASS_RD900_2-4 STAGE_SUS304_NONE</t>
+          <t>Plate, RD900 Bypass 2-4 Stage</t>
         </is>
       </c>
       <c r="D334" t="n">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>RETAINER_BEARING_5208_S45C_NONE</t>
+          <t>Retainer, HD DE Bearing, S45C</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>SLINGER_ID50.0OD77.4L30.9_SUM24L_NONE</t>
+          <t>Slinger, HD550 Rev1 Gear Side</t>
         </is>
       </c>
       <c r="D366" t="n">
@@ -8903,7 +8903,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>SLINGER_ID40.02OD49.6L15.240_12L14_NONE</t>
+          <t>Slinger, HD DE, 15.240±0.005</t>
         </is>
       </c>
       <c r="D369" t="n">
@@ -8926,7 +8926,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>LOCK NUT_FORCED DRIVE_M45X1.5P_S45C_NONE</t>
+          <t>LOCK NUT_FORCED DRIVE_M45X1.5P</t>
         </is>
       </c>
       <c r="D370" t="n">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>RING_LABYRINTH_ID50.00OD70.00L11.2_S45C_NONE</t>
+          <t>RING_LABYRINTH_ID50.00*OD70.00*L11.2_S45C_NONE</t>
         </is>
       </c>
       <c r="D371" t="n">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>ORIFICE_PLATE_D0.3*TUBE 1/4_SUS304_NONE</t>
+          <t>Orifice, Tube Type, D0.3 Tube 1/4</t>
         </is>
       </c>
       <c r="D378" t="n">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>OIL GUIDE_TONGUE SHIM*NON DRIVE_SS400_NONE</t>
+          <t>Tongue Shim-L, MK3000</t>
         </is>
       </c>
       <c r="D390" t="n">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>KEY_MOTOR ROTATOR_RD900_S45C_NONE</t>
+          <t>Key, RD900 22kW Rotator</t>
         </is>
       </c>
       <c r="D396" t="n">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>SPACER_MOTOR ROTATOR_S45C_NONE</t>
+          <t>Ring, RD900/MK3000 Motor Rotator Spacer</t>
         </is>
       </c>
       <c r="D397" t="n">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>PLATE_BYPASS_RD900_2-4 STAGE_SUS304_NONE</t>
+          <t>Plate, RD900 Bypass 2-4 Stage</t>
         </is>
       </c>
       <c r="D399" t="n">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>RETAINER_BEARING_5208_S45C_NONE</t>
+          <t>Retainer, HD DE Bearing, S45C</t>
         </is>
       </c>
       <c r="D436" t="n">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>SLINGER_ID50.0OD77.4L30.9_SUM24L_NONE</t>
+          <t>Slinger, HD550 Rev1 Gear Side</t>
         </is>
       </c>
       <c r="D438" t="n">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>SLINGER_ID40.02OD49.6L15.240_12L14_NONE</t>
+          <t>Slinger, HD DE, 15.240±0.005</t>
         </is>
       </c>
       <c r="D441" t="n">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>ORIFICE_PLATE_D0.3*TUBE 1/4_SUS304_NONE</t>
+          <t>Orifice, Tube Type, D0.3 Tube 1/4</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>LOCK NUT_FORCED DRIVE_M45X1.5P_S45C_NONE</t>
+          <t>LOCK NUT_FORCED DRIVE_M45X1.5P</t>
         </is>
       </c>
       <c r="D446" t="n">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>RING_LABYRINTH_ID50.00OD70.00L11.2_S45C_NONE</t>
+          <t>RING_LABYRINTH_ID50.00*OD70.00*L11.2_S45C_NONE</t>
         </is>
       </c>
       <c r="D451" t="n">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>OIL GUIDE_TONGUE SHIM*NON DRIVE_SS400_NONE</t>
+          <t>Tongue Shim-L, MK3000</t>
         </is>
       </c>
       <c r="D462" t="n">

--- a/STMS_code/dist/매출.xlsx
+++ b/STMS_code/dist/매출.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="일일 품명별 매출" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="일일 총 매출" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="주간 총 매출" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="월간 총 매출" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="분기 총 매출" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="반기 총 매출" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간 총 매출" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일일 품명별 매출" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="일일 총 매출" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주간 총 매출" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월간 총 매출" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기 총 매출" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="반기 총 매출" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간 총 매출" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
